--- a/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/Drop-0_Closure/01_BIBS_Drop-0_Configuration_Inputs_v2.0.xlsx
+++ b/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/Drop-0_Closure/01_BIBS_Drop-0_Configuration_Inputs_v2.0.xlsx
@@ -53994,7 +53994,7 @@
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>Maximum clients a customer search returns before the agent must refine it</t>
+          <t>Maximum clients a customer search returns before the contact centre officer must refine it</t>
         </is>
       </c>
       <c r="G47" s="12" t="inlineStr">

--- a/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/Drop-0_Closure/01_BIBS_Drop-0_Configuration_Inputs_v2.0.xlsx
+++ b/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/Drop-0_Closure/01_BIBS_Drop-0_Configuration_Inputs_v2.0.xlsx
@@ -64,7 +64,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Register'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Migration cross-reference'!$A$4:$H$36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Migration cross-reference'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Lists of values'!$A$4:$L$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Lists of values'!$A$4:$L$138</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Lists of values'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'System parameters'!$A$4:$Q$212</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'System parameters'!$4:$4</definedName>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="D25" s="14" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26">
@@ -28560,7 +28560,7 @@
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>Name and value pairs, as in the example</t>
         </is>
       </c>
       <c r="H88" s="12" t="inlineStr">
@@ -43869,7 +43869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L137"/>
+  <dimension ref="A1:L138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -47359,12 +47359,12 @@
     <row r="70">
       <c r="A70" s="12" t="inlineStr">
         <is>
-          <t>LEGACY_RECORD_TYPE</t>
+          <t>LEGACY_RECORD_STATUS</t>
         </is>
       </c>
       <c r="B70" s="12" t="inlineStr">
         <is>
-          <t>Legacy record type</t>
+          <t>Legacy record status</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
@@ -47383,7 +47383,7 @@
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
@@ -47411,17 +47411,17 @@
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
         <is>
-          <t>MARKET_SEGMENT</t>
+          <t>LEGACY_RECORD_TYPE</t>
         </is>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>Market segment</t>
+          <t>Legacy record type</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Product Maintenance</t>
+          <t>Data Migration</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
@@ -47431,25 +47431,25 @@
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Product Owner, Marketing Business System (MBS)</t>
+          <t>Program Manager, Business Project Services (Data Migration)</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
-          <t>Migration object</t>
+          <t>Template</t>
         </is>
       </c>
       <c r="H71" s="12" t="inlineStr">
         <is>
-          <t>Migration Workbook, object R01, code map LOV:MARKET_SEGMENT</t>
+          <t>This workbook, sheet Lists of values</t>
         </is>
       </c>
       <c r="I71" s="12" t="inlineStr">
         <is>
-          <t>18-Jun-2027 (T-28 weeks)</t>
+          <t>9-Apr-2027 (T-38 weeks)</t>
         </is>
       </c>
       <c r="J71" s="12" t="n"/>
@@ -47463,17 +47463,17 @@
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
         <is>
-          <t>MIG_ACCESS_REASON</t>
+          <t>MARKET_SEGMENT</t>
         </is>
       </c>
       <c r="B72" s="12" t="inlineStr">
         <is>
-          <t>Legacy access reason</t>
+          <t>Market segment</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>Data Migration</t>
+          <t>Product Maintenance</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
@@ -47483,25 +47483,25 @@
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>Program Manager, Business Project Services (Data Migration)</t>
+          <t>Product Owner, Marketing Business System (MBS)</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
-          <t>Template</t>
+          <t>Migration object</t>
         </is>
       </c>
       <c r="H72" s="12" t="inlineStr">
         <is>
-          <t>This workbook, sheet Lists of values</t>
+          <t>Migration Workbook, object R01, code map LOV:MARKET_SEGMENT</t>
         </is>
       </c>
       <c r="I72" s="12" t="inlineStr">
         <is>
-          <t>9-Apr-2027 (T-38 weeks)</t>
+          <t>18-Jun-2027 (T-28 weeks)</t>
         </is>
       </c>
       <c r="J72" s="12" t="n"/>
@@ -47515,12 +47515,12 @@
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
         <is>
-          <t>MIG_BREAK_REASON</t>
+          <t>MIG_ACCESS_REASON</t>
         </is>
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>Reconciliation break reason</t>
+          <t>Legacy access reason</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
@@ -47567,12 +47567,12 @@
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
         <is>
-          <t>MIG_OBJECT_CATEGORY</t>
+          <t>MIG_BREAK_REASON</t>
         </is>
       </c>
       <c r="B74" s="12" t="inlineStr">
         <is>
-          <t>Migration object category</t>
+          <t>Reconciliation break reason</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
@@ -47619,12 +47619,12 @@
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
         <is>
-          <t>MIG_SOURCE_SYSTEM</t>
+          <t>MIG_OBJECT_CATEGORY</t>
         </is>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>Legacy source system</t>
+          <t>Migration object category</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
@@ -47643,7 +47643,7 @@
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
@@ -47671,12 +47671,12 @@
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
         <is>
-          <t>MIG_TRUST_LEVEL</t>
+          <t>MIG_SOURCE_SYSTEM</t>
         </is>
       </c>
       <c r="B76" s="12" t="inlineStr">
         <is>
-          <t>Data trust level</t>
+          <t>Legacy source system</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
@@ -47695,7 +47695,7 @@
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
@@ -47723,12 +47723,12 @@
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
         <is>
-          <t>MIG_WAIVER_REASON</t>
+          <t>MIG_TRUST_LEVEL</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>Row waiver reason</t>
+          <t>Data trust level</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
@@ -47747,7 +47747,7 @@
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
@@ -47775,31 +47775,31 @@
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
         <is>
-          <t>MORTGAGEE_BANK</t>
+          <t>MIG_WAIVER_REASON</t>
         </is>
       </c>
       <c r="B78" s="12" t="inlineStr">
         <is>
-          <t>Mortgagee bank</t>
+          <t>Row waiver reason</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>New Business</t>
+          <t>Data Migration</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>Drop 1</t>
+          <t>Drop 0</t>
         </is>
       </c>
       <c r="E78" s="12" t="inlineStr">
         <is>
-          <t>Product Owner, BDOI (New Business)</t>
+          <t>Program Manager, Business Project Services (Data Migration)</t>
         </is>
       </c>
       <c r="F78" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
@@ -47827,12 +47827,12 @@
     <row r="79">
       <c r="A79" s="12" t="inlineStr">
         <is>
-          <t>NATIONALITY</t>
+          <t>MORTGAGEE_BANK</t>
         </is>
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>Nationality</t>
+          <t>Mortgagee bank</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
@@ -47851,21 +47851,21 @@
         </is>
       </c>
       <c r="F79" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
-          <t>Migration object</t>
+          <t>Template</t>
         </is>
       </c>
       <c r="H79" s="12" t="inlineStr">
         <is>
-          <t>Migration Workbook, object R01, code map LOV:NATIONALITY</t>
+          <t>This workbook, sheet Lists of values</t>
         </is>
       </c>
       <c r="I79" s="12" t="inlineStr">
         <is>
-          <t>18-Jun-2027 (T-28 weeks)</t>
+          <t>9-Apr-2027 (T-38 weeks)</t>
         </is>
       </c>
       <c r="J79" s="12" t="n"/>
@@ -47879,12 +47879,12 @@
     <row r="80">
       <c r="A80" s="12" t="inlineStr">
         <is>
-          <t>OCCUPANCY</t>
+          <t>NATIONALITY</t>
         </is>
       </c>
       <c r="B80" s="12" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Nationality</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
@@ -47907,17 +47907,17 @@
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
-          <t>Template</t>
+          <t>Migration object</t>
         </is>
       </c>
       <c r="H80" s="12" t="inlineStr">
         <is>
-          <t>This workbook, sheet Lists of values</t>
+          <t>Migration Workbook, object R01, code map LOV:NATIONALITY</t>
         </is>
       </c>
       <c r="I80" s="12" t="inlineStr">
         <is>
-          <t>9-Apr-2027 (T-38 weeks)</t>
+          <t>18-Jun-2027 (T-28 weeks)</t>
         </is>
       </c>
       <c r="J80" s="12" t="n"/>
@@ -47931,17 +47931,17 @@
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
         <is>
-          <t>OPS_EXTERNAL_LINK</t>
+          <t>OCCUPANCY</t>
         </is>
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>Operations external link</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>New Business</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
@@ -47951,11 +47951,11 @@
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Head, Operations Services</t>
+          <t>Product Owner, BDOI (New Business)</t>
         </is>
       </c>
       <c r="F81" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
@@ -47983,12 +47983,12 @@
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
         <is>
-          <t>OR_TYPE</t>
+          <t>OPS_EXTERNAL_LINK</t>
         </is>
       </c>
       <c r="B82" s="12" t="inlineStr">
         <is>
-          <t>Official receipt type</t>
+          <t>Operations external link</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
@@ -48007,7 +48007,7 @@
         </is>
       </c>
       <c r="F82" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
@@ -48035,17 +48035,17 @@
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
         <is>
-          <t>PAYEE_CLASS</t>
+          <t>OR_TYPE</t>
         </is>
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>Payee class</t>
+          <t>Official receipt type</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>Accounting, Disbursement and ACSL</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
@@ -48055,7 +48055,7 @@
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>Head, Comptrollership</t>
+          <t>Head, Operations Services</t>
         </is>
       </c>
       <c r="F83" s="12" t="n">
@@ -48063,17 +48063,17 @@
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
-          <t>Migration object</t>
+          <t>Template</t>
         </is>
       </c>
       <c r="H83" s="12" t="inlineStr">
         <is>
-          <t>Migration Workbook, object R01, code map LOV:PAYEE_CLASS</t>
+          <t>This workbook, sheet Lists of values</t>
         </is>
       </c>
       <c r="I83" s="12" t="inlineStr">
         <is>
-          <t>18-Jun-2027 (T-28 weeks)</t>
+          <t>9-Apr-2027 (T-38 weeks)</t>
         </is>
       </c>
       <c r="J83" s="12" t="n"/>
@@ -48087,45 +48087,45 @@
     <row r="84">
       <c r="A84" s="12" t="inlineStr">
         <is>
-          <t>PKG_ADVISORY_GROUP</t>
+          <t>PAYEE_CLASS</t>
         </is>
       </c>
       <c r="B84" s="12" t="inlineStr">
         <is>
-          <t>Advisory recipient group</t>
+          <t>Payee class</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>Product Maintenance</t>
+          <t>Accounting, Disbursement and ACSL</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>Drop 0</t>
+          <t>Drop 1</t>
         </is>
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
-          <t>Product Owner, Marketing Business System (MBS)</t>
+          <t>Head, Comptrollership</t>
         </is>
       </c>
       <c r="F84" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
-          <t>Template</t>
+          <t>Migration object</t>
         </is>
       </c>
       <c r="H84" s="12" t="inlineStr">
         <is>
-          <t>BRD-03 template CI-09, sheet PM-09 Lists and parameters</t>
+          <t>Migration Workbook, object R01, code map LOV:PAYEE_CLASS</t>
         </is>
       </c>
       <c r="I84" s="12" t="inlineStr">
         <is>
-          <t>9-Apr-2027 (T-38 weeks)</t>
+          <t>18-Jun-2027 (T-28 weeks)</t>
         </is>
       </c>
       <c r="J84" s="12" t="n"/>
@@ -48139,12 +48139,12 @@
     <row r="85">
       <c r="A85" s="12" t="inlineStr">
         <is>
-          <t>PKG_NOT_PROCEEDED_REASON</t>
+          <t>PKG_ADVISORY_GROUP</t>
         </is>
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>Package not proceeded reason</t>
+          <t>Advisory recipient group</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
@@ -48191,12 +48191,12 @@
     <row r="86">
       <c r="A86" s="12" t="inlineStr">
         <is>
-          <t>PKG_REQUEST_REASON</t>
+          <t>PKG_NOT_PROCEEDED_REASON</t>
         </is>
       </c>
       <c r="B86" s="12" t="inlineStr">
         <is>
-          <t>Package request reason</t>
+          <t>Package not proceeded reason</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
@@ -48215,7 +48215,7 @@
         </is>
       </c>
       <c r="F86" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
@@ -48243,12 +48243,12 @@
     <row r="87">
       <c r="A87" s="12" t="inlineStr">
         <is>
-          <t>PKG_REQUEST_TYPE</t>
+          <t>PKG_REQUEST_REASON</t>
         </is>
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>Package request type</t>
+          <t>Package request reason</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
@@ -48267,7 +48267,7 @@
         </is>
       </c>
       <c r="F87" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
@@ -48295,12 +48295,12 @@
     <row r="88">
       <c r="A88" s="12" t="inlineStr">
         <is>
-          <t>PKG_RESPONSE_OUTCOME</t>
+          <t>PKG_REQUEST_TYPE</t>
         </is>
       </c>
       <c r="B88" s="12" t="inlineStr">
         <is>
-          <t>Insurer response outcome</t>
+          <t>Package request type</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
@@ -48347,27 +48347,27 @@
     <row r="89">
       <c r="A89" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PAYMENT_MODE</t>
+          <t>PKG_RESPONSE_OUTCOME</t>
         </is>
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>Request payment mode</t>
+          <t>Insurer response outcome</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>Accounting, Disbursement and ACSL</t>
+          <t>Product Maintenance</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>Drop 1</t>
+          <t>Drop 0</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Head, Comptrollership</t>
+          <t>Product Owner, Marketing Business System (MBS)</t>
         </is>
       </c>
       <c r="F89" s="12" t="n">
@@ -48380,7 +48380,7 @@
       </c>
       <c r="H89" s="12" t="inlineStr">
         <is>
-          <t>This workbook, sheet Lists of values</t>
+          <t>BRD-03 template CI-09, sheet PM-09 Lists and parameters</t>
         </is>
       </c>
       <c r="I89" s="12" t="inlineStr">
@@ -48399,12 +48399,12 @@
     <row r="90">
       <c r="A90" s="12" t="inlineStr">
         <is>
-          <t>PRQ_RFP_TYPE</t>
+          <t>PRQ_PAYMENT_MODE</t>
         </is>
       </c>
       <c r="B90" s="12" t="inlineStr">
         <is>
-          <t>Request for payment type</t>
+          <t>Request payment mode</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
@@ -48423,7 +48423,7 @@
         </is>
       </c>
       <c r="F90" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
@@ -48451,17 +48451,17 @@
     <row r="91">
       <c r="A91" s="12" t="inlineStr">
         <is>
-          <t>RECEIPT_CANCEL_REASON</t>
+          <t>PRQ_RFP_TYPE</t>
         </is>
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>Receipt cancellation reason</t>
+          <t>Request for payment type</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Accounting, Disbursement and ACSL</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
@@ -48471,11 +48471,11 @@
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Head, Operations Services</t>
+          <t>Head, Comptrollership</t>
         </is>
       </c>
       <c r="F91" s="12" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
@@ -48503,12 +48503,12 @@
     <row r="92">
       <c r="A92" s="12" t="inlineStr">
         <is>
-          <t>RECON_COMPANY_CONCERNED</t>
+          <t>RECEIPT_CANCEL_REASON</t>
         </is>
       </c>
       <c r="B92" s="12" t="inlineStr">
         <is>
-          <t>Company concerned</t>
+          <t>Receipt cancellation reason</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
@@ -48527,7 +48527,7 @@
         </is>
       </c>
       <c r="F92" s="12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
@@ -48555,12 +48555,12 @@
     <row r="93">
       <c r="A93" s="12" t="inlineStr">
         <is>
-          <t>RECON_DISPOSITION</t>
+          <t>RECON_COMPANY_CONCERNED</t>
         </is>
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>Reconciliation disposition</t>
+          <t>Company concerned</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
@@ -48607,17 +48607,17 @@
     <row r="94">
       <c r="A94" s="12" t="inlineStr">
         <is>
-          <t>REFUND_REASON</t>
+          <t>RECON_DISPOSITION</t>
         </is>
       </c>
       <c r="B94" s="12" t="inlineStr">
         <is>
-          <t>Refund reason</t>
+          <t>Reconciliation disposition</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>Accounting, Disbursement and ACSL</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
@@ -48627,11 +48627,11 @@
       </c>
       <c r="E94" s="12" t="inlineStr">
         <is>
-          <t>Head, Comptrollership</t>
+          <t>Head, Operations Services</t>
         </is>
       </c>
       <c r="F94" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
@@ -48659,17 +48659,17 @@
     <row r="95">
       <c r="A95" s="12" t="inlineStr">
         <is>
-          <t>REINSTATEMENT_REASON</t>
+          <t>REFUND_REASON</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>Reinstatement reason</t>
+          <t>Refund reason</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Accounting, Disbursement and ACSL</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
@@ -48679,11 +48679,11 @@
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>Head, Operations Services</t>
+          <t>Head, Comptrollership</t>
         </is>
       </c>
       <c r="F95" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -48711,12 +48711,12 @@
     <row r="96">
       <c r="A96" s="12" t="inlineStr">
         <is>
-          <t>REMITTANCE_TYPE</t>
+          <t>REINSTATEMENT_REASON</t>
         </is>
       </c>
       <c r="B96" s="12" t="inlineStr">
         <is>
-          <t>Remittance type</t>
+          <t>Reinstatement reason</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
@@ -48735,7 +48735,7 @@
         </is>
       </c>
       <c r="F96" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
@@ -48763,12 +48763,12 @@
     <row r="97">
       <c r="A97" s="12" t="inlineStr">
         <is>
-          <t>REMIT_DEDUCTION_SOURCE</t>
+          <t>REMITTANCE_TYPE</t>
         </is>
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>Remittance deduction source</t>
+          <t>Remittance type</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
@@ -48815,12 +48815,12 @@
     <row r="98">
       <c r="A98" s="12" t="inlineStr">
         <is>
-          <t>REMIT_EXCLUSION_REASON</t>
+          <t>REMIT_DEDUCTION_SOURCE</t>
         </is>
       </c>
       <c r="B98" s="12" t="inlineStr">
         <is>
-          <t>Remittance exclusion reason</t>
+          <t>Remittance deduction source</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
@@ -48839,7 +48839,7 @@
         </is>
       </c>
       <c r="F98" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -48867,12 +48867,12 @@
     <row r="99">
       <c r="A99" s="12" t="inlineStr">
         <is>
-          <t>REMIT_RETURN_REASON</t>
+          <t>REMIT_EXCLUSION_REASON</t>
         </is>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>Remittance return reason</t>
+          <t>Remittance exclusion reason</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
@@ -48891,7 +48891,7 @@
         </is>
       </c>
       <c r="F99" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
@@ -48919,17 +48919,17 @@
     <row r="100">
       <c r="A100" s="12" t="inlineStr">
         <is>
-          <t>RETURN_REASON</t>
+          <t>REMIT_RETURN_REASON</t>
         </is>
       </c>
       <c r="B100" s="12" t="inlineStr">
         <is>
-          <t>Return reason</t>
+          <t>Remittance return reason</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>New Business</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
@@ -48939,11 +48939,11 @@
       </c>
       <c r="E100" s="12" t="inlineStr">
         <is>
-          <t>Product Owner, BDOI (New Business)</t>
+          <t>Head, Operations Services</t>
         </is>
       </c>
       <c r="F100" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
@@ -48971,17 +48971,17 @@
     <row r="101">
       <c r="A101" s="12" t="inlineStr">
         <is>
-          <t>RNW_DISPOSITION</t>
+          <t>RETURN_REASON</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>Renewal disposition</t>
+          <t>Return reason</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>New Business</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
@@ -48991,11 +48991,11 @@
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>Product Owner, Renewal</t>
+          <t>Product Owner, BDOI (New Business)</t>
         </is>
       </c>
       <c r="F101" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -49023,12 +49023,12 @@
     <row r="102">
       <c r="A102" s="12" t="inlineStr">
         <is>
-          <t>RNW_FOLLOWUP_CHANNEL</t>
+          <t>RNW_DISPOSITION</t>
         </is>
       </c>
       <c r="B102" s="12" t="inlineStr">
         <is>
-          <t>Renewal follow-up channel</t>
+          <t>Renewal disposition</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
@@ -49047,7 +49047,7 @@
         </is>
       </c>
       <c r="F102" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
@@ -49075,12 +49075,12 @@
     <row r="103">
       <c r="A103" s="12" t="inlineStr">
         <is>
-          <t>RNW_FOLLOWUP_OUTCOME</t>
+          <t>RNW_FOLLOWUP_CHANNEL</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>Renewal follow-up outcome</t>
+          <t>Renewal follow-up channel</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
@@ -49099,7 +49099,7 @@
         </is>
       </c>
       <c r="F103" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -49127,12 +49127,12 @@
     <row r="104">
       <c r="A104" s="12" t="inlineStr">
         <is>
-          <t>RNW_INSURER_RESPONSE</t>
+          <t>RNW_FOLLOWUP_OUTCOME</t>
         </is>
       </c>
       <c r="B104" s="12" t="inlineStr">
         <is>
-          <t>Insurer renewal response</t>
+          <t>Renewal follow-up outcome</t>
         </is>
       </c>
       <c r="C104" s="12" t="inlineStr">
@@ -49151,7 +49151,7 @@
         </is>
       </c>
       <c r="F104" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
@@ -49179,12 +49179,12 @@
     <row r="105">
       <c r="A105" s="12" t="inlineStr">
         <is>
-          <t>RNW_LAMD_STATUS</t>
+          <t>RNW_INSURER_RESPONSE</t>
         </is>
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>LAMD loan status</t>
+          <t>Insurer renewal response</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
@@ -49203,7 +49203,7 @@
         </is>
       </c>
       <c r="F105" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
@@ -49231,12 +49231,12 @@
     <row r="106">
       <c r="A106" s="12" t="inlineStr">
         <is>
-          <t>RNW_NONRENEWAL_REASON</t>
+          <t>RNW_LAMD_STATUS</t>
         </is>
       </c>
       <c r="B106" s="12" t="inlineStr">
         <is>
-          <t>Reason for Not for Renewal</t>
+          <t>LAMD loan status</t>
         </is>
       </c>
       <c r="C106" s="12" t="inlineStr">
@@ -49255,7 +49255,7 @@
         </is>
       </c>
       <c r="F106" s="12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -49283,12 +49283,12 @@
     <row r="107">
       <c r="A107" s="12" t="inlineStr">
         <is>
-          <t>RNW_OVERRIDE_REASON</t>
+          <t>RNW_NONRENEWAL_REASON</t>
         </is>
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>Renewal override reason</t>
+          <t>Reason for Not for Renewal</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
@@ -49307,7 +49307,7 @@
         </is>
       </c>
       <c r="F107" s="12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
@@ -49335,12 +49335,12 @@
     <row r="108">
       <c r="A108" s="12" t="inlineStr">
         <is>
-          <t>RNW_RETURN_REASON</t>
+          <t>RNW_OVERRIDE_REASON</t>
         </is>
       </c>
       <c r="B108" s="12" t="inlineStr">
         <is>
-          <t>Renewal return reason</t>
+          <t>Renewal override reason</t>
         </is>
       </c>
       <c r="C108" s="12" t="inlineStr">
@@ -49387,12 +49387,12 @@
     <row r="109">
       <c r="A109" s="12" t="inlineStr">
         <is>
-          <t>RNW_TRANSFER_REASON</t>
+          <t>RNW_RETURN_REASON</t>
         </is>
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>Renewal transfer reason</t>
+          <t>Renewal return reason</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
@@ -49411,7 +49411,7 @@
         </is>
       </c>
       <c r="F109" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
@@ -49439,17 +49439,17 @@
     <row r="110">
       <c r="A110" s="12" t="inlineStr">
         <is>
-          <t>RRF_CATEGORY_A</t>
+          <t>RNW_TRANSFER_REASON</t>
         </is>
       </c>
       <c r="B110" s="12" t="inlineStr">
         <is>
-          <t>Refund category A</t>
+          <t>Renewal transfer reason</t>
         </is>
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>Accounting, Disbursement and ACSL</t>
+          <t>Renewal</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
@@ -49459,11 +49459,11 @@
       </c>
       <c r="E110" s="12" t="inlineStr">
         <is>
-          <t>Head, Comptrollership</t>
+          <t>Product Owner, Renewal</t>
         </is>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
@@ -49491,12 +49491,12 @@
     <row r="111">
       <c r="A111" s="12" t="inlineStr">
         <is>
-          <t>RRF_CATEGORY_B</t>
+          <t>RRF_CATEGORY_A</t>
         </is>
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>Refund category B</t>
+          <t>Refund category A</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
@@ -49543,17 +49543,17 @@
     <row r="112">
       <c r="A112" s="12" t="inlineStr">
         <is>
-          <t>SBM_BUCKET</t>
+          <t>RRF_CATEGORY_B</t>
         </is>
       </c>
       <c r="B112" s="12" t="inlineStr">
         <is>
-          <t>Submitted policy bucket</t>
+          <t>Refund category B</t>
         </is>
       </c>
       <c r="C112" s="12" t="inlineStr">
         <is>
-          <t>Submitted Policies</t>
+          <t>Accounting, Disbursement and ACSL</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr">
@@ -49563,11 +49563,11 @@
       </c>
       <c r="E112" s="12" t="inlineStr">
         <is>
-          <t>Product Owner, Submitted Policies</t>
+          <t>Head, Comptrollership</t>
         </is>
       </c>
       <c r="F112" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
@@ -49595,12 +49595,12 @@
     <row r="113">
       <c r="A113" s="12" t="inlineStr">
         <is>
-          <t>SBM_CONVERSION_STATUS</t>
+          <t>SBM_BUCKET</t>
         </is>
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>Conversion status</t>
+          <t>Submitted policy bucket</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
@@ -49619,7 +49619,7 @@
         </is>
       </c>
       <c r="F113" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
@@ -49647,12 +49647,12 @@
     <row r="114">
       <c r="A114" s="12" t="inlineStr">
         <is>
-          <t>SBM_DECLINE_REASON</t>
+          <t>SBM_CONVERSION_STATUS</t>
         </is>
       </c>
       <c r="B114" s="12" t="inlineStr">
         <is>
-          <t>Insurer re-assignment reason</t>
+          <t>Conversion status</t>
         </is>
       </c>
       <c r="C114" s="12" t="inlineStr">
@@ -49671,7 +49671,7 @@
         </is>
       </c>
       <c r="F114" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -49699,12 +49699,12 @@
     <row r="115">
       <c r="A115" s="12" t="inlineStr">
         <is>
-          <t>SBM_IAAF_FINDING</t>
+          <t>SBM_DECLINE_REASON</t>
         </is>
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>Policy review finding</t>
+          <t>Insurer re-assignment reason</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
@@ -49723,7 +49723,7 @@
         </is>
       </c>
       <c r="F115" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
@@ -49751,12 +49751,12 @@
     <row r="116">
       <c r="A116" s="12" t="inlineStr">
         <is>
-          <t>SBM_LETTER_TYPE</t>
+          <t>SBM_IAAF_FINDING</t>
         </is>
       </c>
       <c r="B116" s="12" t="inlineStr">
         <is>
-          <t>Submitted policy letter type</t>
+          <t>Policy review finding</t>
         </is>
       </c>
       <c r="C116" s="12" t="inlineStr">
@@ -49775,7 +49775,7 @@
         </is>
       </c>
       <c r="F116" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
@@ -49803,12 +49803,12 @@
     <row r="117">
       <c r="A117" s="12" t="inlineStr">
         <is>
-          <t>SBM_LOAN_STATUS</t>
+          <t>SBM_LETTER_TYPE</t>
         </is>
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>Loan status</t>
+          <t>Submitted policy letter type</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
@@ -49827,7 +49827,7 @@
         </is>
       </c>
       <c r="F117" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
@@ -49855,12 +49855,12 @@
     <row r="118">
       <c r="A118" s="12" t="inlineStr">
         <is>
-          <t>SBM_NON_RENEWAL_REASON</t>
+          <t>SBM_LOAN_STATUS</t>
         </is>
       </c>
       <c r="B118" s="12" t="inlineStr">
         <is>
-          <t>Non-renewal reason (submitted policy)</t>
+          <t>Loan status</t>
         </is>
       </c>
       <c r="C118" s="12" t="inlineStr">
@@ -49879,7 +49879,7 @@
         </is>
       </c>
       <c r="F118" s="12" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
@@ -49907,12 +49907,12 @@
     <row r="119">
       <c r="A119" s="12" t="inlineStr">
         <is>
-          <t>SBM_REASON</t>
+          <t>SBM_NON_RENEWAL_REASON</t>
         </is>
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>Submitted policy reason</t>
+          <t>Non-renewal reason (submitted policy)</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
@@ -49931,7 +49931,7 @@
         </is>
       </c>
       <c r="F119" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
@@ -49959,12 +49959,12 @@
     <row r="120">
       <c r="A120" s="12" t="inlineStr">
         <is>
-          <t>SBM_RETURN_REASON</t>
+          <t>SBM_REASON</t>
         </is>
       </c>
       <c r="B120" s="12" t="inlineStr">
         <is>
-          <t>IAAF or TOR return reason</t>
+          <t>Submitted policy reason</t>
         </is>
       </c>
       <c r="C120" s="12" t="inlineStr">
@@ -49983,7 +49983,7 @@
         </is>
       </c>
       <c r="F120" s="12" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
@@ -50011,12 +50011,12 @@
     <row r="121">
       <c r="A121" s="12" t="inlineStr">
         <is>
-          <t>SBM_SEGMENT</t>
+          <t>SBM_RETURN_REASON</t>
         </is>
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>Submitted policy segment</t>
+          <t>IAAF or TOR return reason</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
@@ -50063,17 +50063,17 @@
     <row r="122">
       <c r="A122" s="12" t="inlineStr">
         <is>
-          <t>SCR_CASE_TYPE</t>
+          <t>SBM_SEGMENT</t>
         </is>
       </c>
       <c r="B122" s="12" t="inlineStr">
         <is>
-          <t>Screening case type</t>
+          <t>Submitted policy segment</t>
         </is>
       </c>
       <c r="C122" s="12" t="inlineStr">
         <is>
-          <t>Sanction Screening</t>
+          <t>Submitted Policies</t>
         </is>
       </c>
       <c r="D122" s="12" t="inlineStr">
@@ -50083,11 +50083,11 @@
       </c>
       <c r="E122" s="12" t="inlineStr">
         <is>
-          <t>Compliance</t>
+          <t>Product Owner, Submitted Policies</t>
         </is>
       </c>
       <c r="F122" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
@@ -50115,12 +50115,12 @@
     <row r="123">
       <c r="A123" s="12" t="inlineStr">
         <is>
-          <t>SCR_DISPOSITION</t>
+          <t>SCR_CASE_TYPE</t>
         </is>
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>Screening disposition</t>
+          <t>Screening case type</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
@@ -50139,7 +50139,7 @@
         </is>
       </c>
       <c r="F123" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
@@ -50167,12 +50167,12 @@
     <row r="124">
       <c r="A124" s="12" t="inlineStr">
         <is>
-          <t>SCR_DOCUMENT_TYPE</t>
+          <t>SCR_DISPOSITION</t>
         </is>
       </c>
       <c r="B124" s="12" t="inlineStr">
         <is>
-          <t>Screening document type</t>
+          <t>Screening disposition</t>
         </is>
       </c>
       <c r="C124" s="12" t="inlineStr">
@@ -50191,7 +50191,7 @@
         </is>
       </c>
       <c r="F124" s="12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
@@ -50219,12 +50219,12 @@
     <row r="125">
       <c r="A125" s="12" t="inlineStr">
         <is>
-          <t>SCR_FORM_TYPE</t>
+          <t>SCR_DOCUMENT_TYPE</t>
         </is>
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>Screening form type</t>
+          <t>Screening document type</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
@@ -50243,7 +50243,7 @@
         </is>
       </c>
       <c r="F125" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
@@ -50271,12 +50271,12 @@
     <row r="126">
       <c r="A126" s="12" t="inlineStr">
         <is>
-          <t>SCR_LIST_TYPE</t>
+          <t>SCR_FORM_TYPE</t>
         </is>
       </c>
       <c r="B126" s="12" t="inlineStr">
         <is>
-          <t>Watchlist type</t>
+          <t>Screening form type</t>
         </is>
       </c>
       <c r="C126" s="12" t="inlineStr">
@@ -50323,12 +50323,12 @@
     <row r="127">
       <c r="A127" s="12" t="inlineStr">
         <is>
-          <t>SCR_REASSIGN_REASON</t>
+          <t>SCR_LIST_TYPE</t>
         </is>
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>Case re-assignment reason</t>
+          <t>Watchlist type</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
@@ -50375,12 +50375,12 @@
     <row r="128">
       <c r="A128" s="12" t="inlineStr">
         <is>
-          <t>SCR_STR_REASON</t>
+          <t>SCR_REASSIGN_REASON</t>
         </is>
       </c>
       <c r="B128" s="12" t="inlineStr">
         <is>
-          <t>STR reason</t>
+          <t>Case re-assignment reason</t>
         </is>
       </c>
       <c r="C128" s="12" t="inlineStr">
@@ -50399,7 +50399,7 @@
         </is>
       </c>
       <c r="F128" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
@@ -50427,17 +50427,17 @@
     <row r="129">
       <c r="A129" s="12" t="inlineStr">
         <is>
-          <t>SERVICE_FEE_SEGMENT</t>
+          <t>SCR_STR_REASON</t>
         </is>
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>Service fee segment</t>
+          <t>STR reason</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>Accounting, Disbursement and ACSL</t>
+          <t>Sanction Screening</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
@@ -50447,11 +50447,11 @@
       </c>
       <c r="E129" s="12" t="inlineStr">
         <is>
-          <t>Head, Comptrollership</t>
+          <t>Compliance</t>
         </is>
       </c>
       <c r="F129" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
@@ -50479,17 +50479,17 @@
     <row r="130">
       <c r="A130" s="12" t="inlineStr">
         <is>
-          <t>SOURCE_CHANNEL</t>
+          <t>SERVICE_FEE_SEGMENT</t>
         </is>
       </c>
       <c r="B130" s="12" t="inlineStr">
         <is>
-          <t>Source channel</t>
+          <t>Service fee segment</t>
         </is>
       </c>
       <c r="C130" s="12" t="inlineStr">
         <is>
-          <t>New Business</t>
+          <t>Accounting, Disbursement and ACSL</t>
         </is>
       </c>
       <c r="D130" s="12" t="inlineStr">
@@ -50499,25 +50499,25 @@
       </c>
       <c r="E130" s="12" t="inlineStr">
         <is>
-          <t>Product Owner, BDOI (New Business)</t>
+          <t>Head, Comptrollership</t>
         </is>
       </c>
       <c r="F130" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
-          <t>Migration object</t>
+          <t>Template</t>
         </is>
       </c>
       <c r="H130" s="12" t="inlineStr">
         <is>
-          <t>Migration Workbook, object R01, code map MIS:BUSINESS_ORIGIN</t>
+          <t>This workbook, sheet Lists of values</t>
         </is>
       </c>
       <c r="I130" s="12" t="inlineStr">
         <is>
-          <t>18-Jun-2027 (T-28 weeks)</t>
+          <t>9-Apr-2027 (T-38 weeks)</t>
         </is>
       </c>
       <c r="J130" s="12" t="n"/>
@@ -50531,12 +50531,12 @@
     <row r="131">
       <c r="A131" s="12" t="inlineStr">
         <is>
-          <t>SOURCE_OF_FUNDS</t>
+          <t>SOURCE_CHANNEL</t>
         </is>
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>Source of funds</t>
+          <t>Source channel</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
@@ -50555,7 +50555,7 @@
         </is>
       </c>
       <c r="F131" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
@@ -50564,7 +50564,7 @@
       </c>
       <c r="H131" s="12" t="inlineStr">
         <is>
-          <t>Migration Workbook, object R01, code map LOV:SOURCE_OF_FUNDS</t>
+          <t>Migration Workbook, object R01, code map MIS:BUSINESS_ORIGIN</t>
         </is>
       </c>
       <c r="I131" s="12" t="inlineStr">
@@ -50583,17 +50583,17 @@
     <row r="132">
       <c r="A132" s="12" t="inlineStr">
         <is>
-          <t>SPECIAL_REMIT_CONDITION</t>
+          <t>SOURCE_OF_FUNDS</t>
         </is>
       </c>
       <c r="B132" s="12" t="inlineStr">
         <is>
-          <t>Special remittance condition</t>
+          <t>Source of funds</t>
         </is>
       </c>
       <c r="C132" s="12" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>New Business</t>
         </is>
       </c>
       <c r="D132" s="12" t="inlineStr">
@@ -50603,25 +50603,25 @@
       </c>
       <c r="E132" s="12" t="inlineStr">
         <is>
-          <t>Head, Operations Services</t>
+          <t>Product Owner, BDOI (New Business)</t>
         </is>
       </c>
       <c r="F132" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
-          <t>Template</t>
+          <t>Migration object</t>
         </is>
       </c>
       <c r="H132" s="12" t="inlineStr">
         <is>
-          <t>This workbook, sheet Lists of values</t>
+          <t>Migration Workbook, object R01, code map LOV:SOURCE_OF_FUNDS</t>
         </is>
       </c>
       <c r="I132" s="12" t="inlineStr">
         <is>
-          <t>9-Apr-2027 (T-38 weeks)</t>
+          <t>18-Jun-2027 (T-28 weeks)</t>
         </is>
       </c>
       <c r="J132" s="12" t="n"/>
@@ -50635,31 +50635,31 @@
     <row r="133">
       <c r="A133" s="12" t="inlineStr">
         <is>
-          <t>UAM_BUSINESS_UNIT</t>
+          <t>SPECIAL_REMIT_CONDITION</t>
         </is>
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>Business unit group</t>
+          <t>Special remittance condition</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>User Access Maintenance</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>Drop 0</t>
+          <t>Drop 1</t>
         </is>
       </c>
       <c r="E133" s="12" t="inlineStr">
         <is>
-          <t>Business Administration (User Access)</t>
+          <t>Head, Operations Services</t>
         </is>
       </c>
       <c r="F133" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
@@ -50668,7 +50668,7 @@
       </c>
       <c r="H133" s="12" t="inlineStr">
         <is>
-          <t>BRD-11 template CI-06, sheet UA-06 Lists of values</t>
+          <t>This workbook, sheet Lists of values</t>
         </is>
       </c>
       <c r="I133" s="12" t="inlineStr">
@@ -50687,12 +50687,12 @@
     <row r="134">
       <c r="A134" s="12" t="inlineStr">
         <is>
-          <t>UAM_DEACTIVATION_REASON</t>
+          <t>UAM_BUSINESS_UNIT</t>
         </is>
       </c>
       <c r="B134" s="12" t="inlineStr">
         <is>
-          <t>User deactivation reason</t>
+          <t>Business unit group</t>
         </is>
       </c>
       <c r="C134" s="12" t="inlineStr">
@@ -50711,7 +50711,7 @@
         </is>
       </c>
       <c r="F134" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
@@ -50739,12 +50739,12 @@
     <row r="135">
       <c r="A135" s="12" t="inlineStr">
         <is>
-          <t>UAM_USER_LEVEL</t>
+          <t>UAM_DEACTIVATION_REASON</t>
         </is>
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t>User level</t>
+          <t>User deactivation reason</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
@@ -50763,7 +50763,7 @@
         </is>
       </c>
       <c r="F135" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
@@ -50791,31 +50791,31 @@
     <row r="136">
       <c r="A136" s="12" t="inlineStr">
         <is>
-          <t>VEHICLE_BODY_TYPE</t>
+          <t>UAM_USER_LEVEL</t>
         </is>
       </c>
       <c r="B136" s="12" t="inlineStr">
         <is>
-          <t>Vehicle body type</t>
+          <t>User level</t>
         </is>
       </c>
       <c r="C136" s="12" t="inlineStr">
         <is>
-          <t>New Business</t>
+          <t>User Access Maintenance</t>
         </is>
       </c>
       <c r="D136" s="12" t="inlineStr">
         <is>
-          <t>Drop 1</t>
+          <t>Drop 0</t>
         </is>
       </c>
       <c r="E136" s="12" t="inlineStr">
         <is>
-          <t>Product Owner, BDOI (New Business)</t>
+          <t>Business Administration (User Access)</t>
         </is>
       </c>
       <c r="F136" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G136" s="12" t="inlineStr">
         <is>
@@ -50824,7 +50824,7 @@
       </c>
       <c r="H136" s="12" t="inlineStr">
         <is>
-          <t>This workbook, sheet Lists of values</t>
+          <t>BRD-11 template CI-06, sheet UA-06 Lists of values</t>
         </is>
       </c>
       <c r="I136" s="12" t="inlineStr">
@@ -50843,17 +50843,17 @@
     <row r="137">
       <c r="A137" s="12" t="inlineStr">
         <is>
-          <t>VOID_REASON</t>
+          <t>VEHICLE_BODY_TYPE</t>
         </is>
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>Void reason</t>
+          <t>Vehicle body type</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>New Business</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
@@ -50863,11 +50863,11 @@
       </c>
       <c r="E137" s="12" t="inlineStr">
         <is>
-          <t>Head, Operations Services</t>
+          <t>Product Owner, BDOI (New Business)</t>
         </is>
       </c>
       <c r="F137" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
@@ -50892,21 +50892,73 @@
       </c>
       <c r="L137" s="12" t="n"/>
     </row>
+    <row r="138">
+      <c r="A138" s="12" t="inlineStr">
+        <is>
+          <t>VOID_REASON</t>
+        </is>
+      </c>
+      <c r="B138" s="12" t="inlineStr">
+        <is>
+          <t>Void reason</t>
+        </is>
+      </c>
+      <c r="C138" s="12" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D138" s="12" t="inlineStr">
+        <is>
+          <t>Drop 1</t>
+        </is>
+      </c>
+      <c r="E138" s="12" t="inlineStr">
+        <is>
+          <t>Head, Operations Services</t>
+        </is>
+      </c>
+      <c r="F138" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G138" s="12" t="inlineStr">
+        <is>
+          <t>Template</t>
+        </is>
+      </c>
+      <c r="H138" s="12" t="inlineStr">
+        <is>
+          <t>This workbook, sheet Lists of values</t>
+        </is>
+      </c>
+      <c r="I138" s="12" t="inlineStr">
+        <is>
+          <t>9-Apr-2027 (T-38 weeks)</t>
+        </is>
+      </c>
+      <c r="J138" s="12" t="n"/>
+      <c r="K138" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L138" s="12" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:L137"/>
+  <autoFilter ref="A4:L138"/>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:L637">
+  <conditionalFormatting sqref="A5:L638">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="G5:G637" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Route" error="Choose a value from the list (Route)." type="list">
+    <dataValidation sqref="G5:G638" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Route" error="Choose a value from the list (Route)." type="list">
       <formula1>'_lists'!$C$1:$C$3</formula1>
     </dataValidation>
-    <dataValidation sqref="K5:K637" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
+    <dataValidation sqref="K5:K638" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
       <formula1>'_lists'!$D$1:$D$5</formula1>
     </dataValidation>
   </dataValidations>
